--- a/st1.xlsx
+++ b/st1.xlsx
@@ -425,277 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rig</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Date for Rig-up</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Well site Number</t>
+          <t>Secondary_Info</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Date for Rig-down</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Feild Name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Asset Name</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Log Suite</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Well site Submission</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LQC</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Post processed product</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Date of submission</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>No. of prints</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LQC(Acceptable/Not Acceptable)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Remarks</t>
+          <t>Date_Info</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADMARINE 09</t>
+          <t>Well</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>Well Name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAWH OO C«SdRR</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>Rig-up</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Rig-up Date</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADMARINE 09</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>Rig</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rig Name/Number</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Rig-down</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[MHS SSSC*SON.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>Rig-down Date</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SKDOOZOH-250602</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3-5" &amp; 2.25" DUMMY-CCL (DD) &amp; 2" SPLIT SHOT CUTTER-CCL LOG</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SO Number</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SO Number Details</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Well: | [SAWH OO C«SdRRigup: |</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6-Jun-25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6-Jun-25</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Acceptable</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3-5" &amp; 2.25" DUMMY-CCL (DD) &amp; 2" SPLIT SHOT CUTTER-CCL LOG | NA |</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6-Jun-25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>6-Jun-25</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Acceptable</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>['M/s HLSA certifies that all deliverables are submitted to Logging Services, ONGC, Mumbai as per technical specifications of Contract 9010035393 and as per Table-E of Specifications.', 'wn Ne Ca Sigrature: \\S M/s HLSA Refrepresentative Sigaature Lite , TBBlace (ONGC Representative)']</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Asset Name</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Log Suite</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Log Suite Details</t>
         </is>
       </c>
     </row>

--- a/st1.xlsx
+++ b/st1.xlsx
@@ -425,116 +425,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>section</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Secondary_Info</t>
+          <t>details</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Date_Info</t>
+          <t>secondary_info</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>date_info</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Details of Deliverable</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Well</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Well Name</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Rig-up</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Rig-up Date</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>05/06/2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Details of Deliverable</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Rig</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rig Name/Number</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>ADMARINE 09</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Rig-down</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Rig-down Date</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Details of Deliverable</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Field Name</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>SO Number</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SO Number Details</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Details of Deliverable</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Asset Name</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Log Suite</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Log Suite Details</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
